--- a/data/trans_orig/P36B05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36B05-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10891</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25880</t>
+          <t>26758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15979</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36464</t>
+          <t>36376</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31949</t>
+          <t>31415</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57126</t>
+          <t>57718</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105920</t>
+          <t>107062</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147564</t>
+          <t>148360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112519</t>
+          <t>110746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158421</t>
+          <t>154530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>231421</t>
+          <t>229723</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>289716</t>
+          <t>290531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>564418</t>
+          <t>563726</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>631279</t>
+          <t>629062</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>717190</t>
+          <t>716473</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>790349</t>
+          <t>789937</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1303127</t>
+          <t>1305287</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1393743</t>
+          <t>1404565</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,9%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>228630</t>
+          <t>230258</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>284408</t>
+          <t>286362</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>336933</t>
+          <t>338498</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>401601</t>
+          <t>405481</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>587989</t>
+          <t>586326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>670960</t>
+          <t>669298</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23682</t>
+          <t>22411</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45905</t>
+          <t>44796</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>21355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44216</t>
+          <t>43854</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50014</t>
+          <t>48155</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80345</t>
+          <t>80645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19653</t>
+          <t>18713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30695</t>
+          <t>30721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21539</t>
+          <t>20652</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42908</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>100742</t>
+          <t>98752</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141102</t>
+          <t>142021</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88397</t>
+          <t>87630</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129480</t>
+          <t>129088</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>196970</t>
+          <t>195952</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>255960</t>
+          <t>255861</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>868794</t>
+          <t>869261</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>955532</t>
+          <t>950661</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>866722</t>
+          <t>865543</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>947703</t>
+          <t>947717</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1758675</t>
+          <t>1756538</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1873434</t>
+          <t>1878711</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>564349</t>
+          <t>564218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>645162</t>
+          <t>643038</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>475914</t>
+          <t>474263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>553901</t>
+          <t>550866</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1063457</t>
+          <t>1061249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1171173</t>
+          <t>1172512</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33615</t>
+          <t>33798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60273</t>
+          <t>60481</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28680</t>
+          <t>27910</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53441</t>
+          <t>54468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66278</t>
+          <t>68204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>103479</t>
+          <t>102321</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15091</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22298</t>
+          <t>22967</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51084</t>
+          <t>50685</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19774</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40866</t>
+          <t>41217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48358</t>
+          <t>50019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82092</t>
+          <t>84237</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>277297</t>
+          <t>274794</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>324499</t>
+          <t>323756</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>261343</t>
+          <t>264256</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>305405</t>
+          <t>307347</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>552119</t>
+          <t>549264</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>614960</t>
+          <t>615126</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162668</t>
+          <t>167385</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>208025</t>
+          <t>210900</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>128915</t>
+          <t>130016</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>170298</t>
+          <t>170520</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>306868</t>
+          <t>310619</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>366215</t>
+          <t>371499</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30977</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38849</t>
+          <t>39004</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25761</t>
+          <t>25207</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47408</t>
+          <t>48370</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>37522</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66581</t>
+          <t>65343</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70317</t>
+          <t>69195</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>108423</t>
+          <t>105964</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251966</t>
+          <t>253119</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>317756</t>
+          <t>317840</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240826</t>
+          <t>237951</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>302683</t>
+          <t>304795</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>509626</t>
+          <t>506883</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>596046</t>
+          <t>599954</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1747390</t>
+          <t>1753914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1864735</t>
+          <t>1868908</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1885840</t>
+          <t>1888159</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2001261</t>
+          <t>2002737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3682400</t>
+          <t>3674378</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3839543</t>
+          <t>3842181</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>995956</t>
+          <t>995314</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1100105</t>
+          <t>1100043</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>983126</t>
+          <t>986570</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1088754</t>
+          <t>1086186</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2001844</t>
+          <t>2004437</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2156995</t>
+          <t>2161825</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>80339</t>
+          <t>81005</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121158</t>
+          <t>121698</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58748</t>
+          <t>60244</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>93916</t>
+          <t>94340</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>150909</t>
+          <t>150621</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>202149</t>
+          <t>201615</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21104</t>
+          <t>20585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>42917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32715</t>
+          <t>31994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37907</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66319</t>
+          <t>68029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143950</t>
+          <t>144729</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>193702</t>
+          <t>193115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186340</t>
+          <t>185376</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239984</t>
+          <t>239543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343004</t>
+          <t>343132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>417683</t>
+          <t>416640</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>508928</t>
+          <t>504269</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>573976</t>
+          <t>570602</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>717465</t>
+          <t>717877</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>793591</t>
+          <t>791384</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1243411</t>
+          <t>1245320</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1342412</t>
+          <t>1345600</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,34%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>199618</t>
+          <t>198491</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>253225</t>
+          <t>253539</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>300795</t>
+          <t>299004</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>364654</t>
+          <t>366417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>512113</t>
+          <t>511197</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>597213</t>
+          <t>596830</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19565</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27104</t>
+          <t>27143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17995</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41132</t>
+          <t>39491</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12550</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32148</t>
+          <t>32067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25475</t>
+          <t>25860</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24258</t>
+          <t>23084</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48219</t>
+          <t>49676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112196</t>
+          <t>110033</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156283</t>
+          <t>157788</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115868</t>
+          <t>115872</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>163158</t>
+          <t>163199</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242044</t>
+          <t>241397</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306451</t>
+          <t>304750</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1010164</t>
+          <t>1009158</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1097872</t>
+          <t>1099413</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932463</t>
+          <t>930404</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1019295</t>
+          <t>1015810</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1964391</t>
+          <t>1959583</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2089030</t>
+          <t>2095385</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>652374</t>
+          <t>652898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>742692</t>
+          <t>738140</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>534346</t>
+          <t>537968</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>617346</t>
+          <t>619265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1216153</t>
+          <t>1210260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1337060</t>
+          <t>1334437</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48072</t>
+          <t>47811</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>79902</t>
+          <t>80096</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37018</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62856</t>
+          <t>63889</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>90787</t>
+          <t>90040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131951</t>
+          <t>130277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15970</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34304</t>
+          <t>33237</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>29008</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54878</t>
+          <t>56201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47297</t>
+          <t>46560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82145</t>
+          <t>80225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>240546</t>
+          <t>238539</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>284934</t>
+          <t>286353</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>237935</t>
+          <t>237144</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>282697</t>
+          <t>280779</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>485417</t>
+          <t>490301</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>552498</t>
+          <t>557518</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,52%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>143615</t>
+          <t>141781</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>186408</t>
+          <t>186716</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126126</t>
+          <t>125585</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>168938</t>
+          <t>167293</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>283224</t>
+          <t>280217</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>342577</t>
+          <t>342924</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38653</t>
+          <t>39146</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24935</t>
+          <t>25144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50272</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41109</t>
+          <t>41469</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70841</t>
+          <t>72802</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27253</t>
+          <t>26715</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54019</t>
+          <t>53359</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73840</t>
+          <t>75379</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114047</t>
+          <t>118114</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>289704</t>
+          <t>289768</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>364111</t>
+          <t>358825</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>352853</t>
+          <t>351387</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>427296</t>
+          <t>432107</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>658085</t>
+          <t>661080</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>763544</t>
+          <t>772772</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1794156</t>
+          <t>1792018</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1913124</t>
+          <t>1914062</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1924777</t>
+          <t>1931114</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2053315</t>
+          <t>2049375</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3761214</t>
+          <t>3752193</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3929751</t>
+          <t>3923504</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1027192</t>
+          <t>1031570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1142698</t>
+          <t>1141108</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>999950</t>
+          <t>996878</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1112590</t>
+          <t>1111193</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2061375</t>
+          <t>2053424</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2213846</t>
+          <t>2216683</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>79820</t>
+          <t>81349</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>121390</t>
+          <t>119928</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59886</t>
+          <t>59849</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94817</t>
+          <t>93334</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>150275</t>
+          <t>148828</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>202559</t>
+          <t>203031</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17905</t>
+          <t>18760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38398</t>
+          <t>39180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12692</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33018</t>
+          <t>32396</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>35423</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64624</t>
+          <t>64053</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108962</t>
+          <t>109816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>149969</t>
+          <t>147092</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186703</t>
+          <t>184736</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>239586</t>
+          <t>240787</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305681</t>
+          <t>307284</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>373497</t>
+          <t>373382</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>388489</t>
+          <t>388465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>442372</t>
+          <t>439509</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>510968</t>
+          <t>513327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>579089</t>
+          <t>577220</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>923607</t>
+          <t>917311</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1006458</t>
+          <t>1004184</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,47%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136031</t>
+          <t>138186</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>180092</t>
+          <t>182081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>156067</t>
+          <t>154526</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>205970</t>
+          <t>206092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>303523</t>
+          <t>303052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>372984</t>
+          <t>374287</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37219</t>
+          <t>35890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24272</t>
+          <t>24128</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50465</t>
+          <t>47819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44806</t>
+          <t>45250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77293</t>
+          <t>77294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26472</t>
+          <t>25156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,82 +7348,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>21394</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12514</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33908</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>37389</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>25708</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>52018</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>1,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>21394</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13495</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>34962</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>37389</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>26402</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>51298</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189632</t>
+          <t>186313</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>246433</t>
+          <t>246369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>179112</t>
+          <t>178777</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232993</t>
+          <t>233575</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>383563</t>
+          <t>382712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>462205</t>
+          <t>464399</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1130539</t>
+          <t>1130420</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1225666</t>
+          <t>1224318</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1129600</t>
+          <t>1127624</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1219686</t>
+          <t>1216934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2292883</t>
+          <t>2286985</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2416147</t>
+          <t>2413199</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,53%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>545239</t>
+          <t>544660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>630399</t>
+          <t>630285</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>476763</t>
+          <t>476603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>550679</t>
+          <t>555535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1042336</t>
+          <t>1038941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1160220</t>
+          <t>1157404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59187</t>
+          <t>60626</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>94170</t>
+          <t>96540</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>53638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85299</t>
+          <t>88364</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>123171</t>
+          <t>123614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170681</t>
+          <t>172741</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12411</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39836</t>
+          <t>40501</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69009</t>
+          <t>68938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40059</t>
+          <t>37185</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66549</t>
+          <t>65883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87429</t>
+          <t>85390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127747</t>
+          <t>124936</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>290310</t>
+          <t>287781</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>336107</t>
+          <t>333460</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>317282</t>
+          <t>319847</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>363636</t>
+          <t>362609</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>620951</t>
+          <t>620582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>685752</t>
+          <t>686466</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,63%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>143051</t>
+          <t>146053</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>188372</t>
+          <t>189661</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>121996</t>
+          <t>122692</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>162554</t>
+          <t>163450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>280089</t>
+          <t>278140</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>338864</t>
+          <t>338112</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>23893</t>
+          <t>22392</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21276</t>
+          <t>19322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37593</t>
+          <t>34994</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33713</t>
+          <t>32616</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59555</t>
+          <t>59336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>33391</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62831</t>
+          <t>63696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74742</t>
+          <t>74640</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>113594</t>
+          <t>113291</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>361449</t>
+          <t>362106</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>438085</t>
+          <t>437032</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>426239</t>
+          <t>426612</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>509631</t>
+          <t>511868</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>811040</t>
+          <t>810440</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>922797</t>
+          <t>923993</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1846838</t>
+          <t>1844591</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1961048</t>
+          <t>1958355</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2005087</t>
+          <t>2005484</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2125156</t>
+          <t>2125204</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3894401</t>
+          <t>3885161</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4049459</t>
+          <t>4052380</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>859351</t>
+          <t>857034</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>963875</t>
+          <t>961368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>780485</t>
+          <t>785930</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>883414</t>
+          <t>882832</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1678544</t>
+          <t>1664680</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1823716</t>
+          <t>1816176</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>94222</t>
+          <t>93586</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138464</t>
+          <t>136909</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>94953</t>
+          <t>93451</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>138565</t>
+          <t>136454</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>197559</t>
+          <t>199317</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>258211</t>
+          <t>258578</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>15091</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7297</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>24152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10553</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>17016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23125</t>
+          <t>26197</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17275</t>
+          <t>18674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31620</t>
+          <t>36669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59824</t>
+          <t>65298</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47455</t>
+          <t>51771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73909</t>
+          <t>79704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>107378</t>
+          <t>112461</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92877</t>
+          <t>98779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123862</t>
+          <t>126799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>167203</t>
+          <t>177759</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149723</t>
+          <t>159212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>193643</t>
+          <t>197623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>278251</t>
+          <t>302432</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>257583</t>
+          <t>276861</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>297998</t>
+          <t>324338</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>380592</t>
+          <t>409519</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>358920</t>
+          <t>389059</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>401543</t>
+          <t>432456</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>658843</t>
+          <t>711950</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>626158</t>
+          <t>679931</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>687550</t>
+          <t>742070</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>150335</t>
+          <t>180276</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>131770</t>
+          <t>160393</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>169172</t>
+          <t>202030</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>240888</t>
+          <t>269923</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>221934</t>
+          <t>249374</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>262000</t>
+          <t>292442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>391224</t>
+          <t>450199</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361063</t>
+          <t>422678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>417871</t>
+          <t>479490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>14284</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7436</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21995</t>
+          <t>24814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15345</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>26409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>32495</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>22788</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40015</t>
+          <t>43433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>513798</t>
+          <t>577381</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>513798</t>
+          <t>577381</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>513798</t>
+          <t>577381</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>754756</t>
+          <t>821219</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>754756</t>
+          <t>821219</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>754756</t>
+          <t>821219</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1268554</t>
+          <t>1398600</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1268554</t>
+          <t>1398600</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1268554</t>
+          <t>1398600</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>20478</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>32960</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16185</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25554</t>
+          <t>31037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>29487</t>
+          <t>41345</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>30203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41417</t>
+          <t>54902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84157</t>
+          <t>90654</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58087</t>
+          <t>73927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105492</t>
+          <t>109232</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>114057</t>
+          <t>131901</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80537</t>
+          <t>110897</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140904</t>
+          <t>155976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>198214</t>
+          <t>222555</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156759</t>
+          <t>193650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>232523</t>
+          <t>251800</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1134185</t>
+          <t>1201223</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>819097</t>
+          <t>1144995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1287914</t>
+          <t>1255829</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1371707</t>
+          <t>1239059</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1246685</t>
+          <t>1197962</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1610720</t>
+          <t>1279574</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2505891</t>
+          <t>2440283</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2118837</t>
+          <t>2374871</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2762249</t>
+          <t>2508609</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>57,03%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>758009</t>
+          <t>851828</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>562642</t>
+          <t>795613</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>874109</t>
+          <t>904880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>701463</t>
+          <t>729454</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>516014</t>
+          <t>692548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>830162</t>
+          <t>768764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1459472</t>
+          <t>1581282</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1161249</t>
+          <t>1516141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1645952</t>
+          <t>1652130</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>300043</t>
+          <t>65772</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56816</t>
+          <t>49326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>791249</t>
+          <t>85536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>47544</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20578</t>
+          <t>33558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>46471</t>
+          <t>63866</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>332454</t>
+          <t>113316</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>86225</t>
+          <t>92503</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1037510</t>
+          <t>138136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2289695</t>
+          <t>2229956</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2289695</t>
+          <t>2229956</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2289695</t>
+          <t>2229956</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2235824</t>
+          <t>2168824</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2235824</t>
+          <t>2168824</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2235824</t>
+          <t>2168824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4525518</t>
+          <t>4398781</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4525518</t>
+          <t>4398781</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4525518</t>
+          <t>4398781</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>9821</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23465</t>
+          <t>24236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10455</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>26905</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>59152</t>
+          <t>62045</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46503</t>
+          <t>48325</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74751</t>
+          <t>78755</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>78583</t>
+          <t>87527</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64204</t>
+          <t>72480</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94552</t>
+          <t>105186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>137734</t>
+          <t>149571</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118235</t>
+          <t>129883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>158105</t>
+          <t>171011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>369246</t>
+          <t>409462</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>340993</t>
+          <t>380234</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>396585</t>
+          <t>435716</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>388436</t>
+          <t>425979</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>367549</t>
+          <t>400789</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>410103</t>
+          <t>449007</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>757683</t>
+          <t>835441</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>720051</t>
+          <t>798244</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>790529</t>
+          <t>875196</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>60,51%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>193915</t>
+          <t>218617</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>170876</t>
+          <t>192335</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>219824</t>
+          <t>247096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>172643</t>
+          <t>196913</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>153410</t>
+          <t>175813</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193315</t>
+          <t>219632</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>366558</t>
+          <t>415530</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>334527</t>
+          <t>380896</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>399050</t>
+          <t>449168</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,05%</t>
         </is>
       </c>
     </row>
@@ -11421,22 +11421,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55841</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>14479</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>28204</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>18564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>64631</t>
+          <t>41701</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>27942</t>
+          <t>37703</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19320</t>
+          <t>25897</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42012</t>
+          <t>51389</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>41276</t>
+          <t>47557</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>37447</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52441</t>
+          <t>60063</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>69218</t>
+          <t>85260</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55295</t>
+          <t>71184</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85842</t>
+          <t>105636</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>203133</t>
+          <t>217997</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>160244</t>
+          <t>190265</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>236451</t>
+          <t>244352</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>300018</t>
+          <t>331888</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>244206</t>
+          <t>305227</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>339642</t>
+          <t>365891</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>503151</t>
+          <t>549885</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>434952</t>
+          <t>509113</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>560003</t>
+          <t>594003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1781682</t>
+          <t>1913118</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1369508</t>
+          <t>1844947</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1940998</t>
+          <t>1981584</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2140735</t>
+          <t>2074557</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2003519</t>
+          <t>2012680</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2384080</t>
+          <t>2120864</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3922418</t>
+          <t>3987675</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3508732</t>
+          <t>3909985</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4193763</t>
+          <t>4080455</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1102259</t>
+          <t>1250722</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>836835</t>
+          <t>1185112</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1208024</t>
+          <t>1314526</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1114995</t>
+          <t>1196289</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>947635</t>
+          <t>1152023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1253960</t>
+          <t>1251356</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2217254</t>
+          <t>2447012</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1926191</t>
+          <t>2361778</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2398502</t>
+          <t>2527676</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>335100</t>
+          <t>99385</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>91652</t>
+          <t>78467</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1121979</t>
+          <t>123030</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>54019</t>
+          <t>74629</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40682</t>
+          <t>57404</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70495</t>
+          <t>92266</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>389119</t>
+          <t>174014</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>138201</t>
+          <t>146620</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1242680</t>
+          <t>205184</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3450116</t>
+          <t>3518925</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3450116</t>
+          <t>3518925</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3450116</t>
+          <t>3518925</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3651043</t>
+          <t>3724920</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3651043</t>
+          <t>3724920</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3651043</t>
+          <t>3724920</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7101159</t>
+          <t>7243845</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7101159</t>
+          <t>7243845</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7101159</t>
+          <t>7243845</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
